--- a/kawasaki_project/05_試算・管理シート/川崎町_他メンバー素案との対比_論点整理_R8.10.16.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_他メンバー素案との対比_論点整理_R8.10.16.xlsx
@@ -724,27 +724,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>181</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>資料編と奥付の取り扱い</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>第9期計画書は98〜102頁に資料編（①川崎町介護保険条例の抜粋②川崎町介護保険運営委員会規則③委員名簿④策定経過の概要）を置き、108頁に奥付（編集／川崎町 保健福祉課 介護保険係、住所・電話・ファクス）を置いています。**当方の計画素案には、いずれもまだありません。** 次の3点をご確認ください。①資料編を計画書の本体に組み込むか、別冊とするか②条例・規則の現行の条文及び第10期の委員名簿のご提供③奥付の課名・住所・電話番号・ファクス番号。⚠ **委員名簿は委員の氏名を含むため、当方では起こしません**（個人情報を当方の成果品に転記しない方針によります）。⚠ 資料編を13頁と見込み、圧縮案の頁数（本文109頁＋資料編13頁＝122頁）に織り込んでいます。頁数が変われば圧縮の度合いも変わります（確認事項No.83と併せてご判断ください）。</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>既に登録済み</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>既定値＝第9期計画書の構成に倣い、資料編を計画書の本体に組み込む前提で頁数を見込みます。条文・名簿のご提供がない間は枠のみを置き、推測で埋めません。</t>
         </is>
